--- a/src/时序数据预测-系列/单元时序预测-水质参数/Tb/data/样点4.xlsx
+++ b/src/时序数据预测-系列/单元时序预测-水质参数/Tb/data/样点4.xlsx
@@ -5,15 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xxqhh\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xxqhh\Desktop\Tb-云量50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65F5D2C8-B647-44DA-B116-D563559B7DFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6D8F4CC-4B5A-4DFB-85D7-11530A436BD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="样点5" sheetId="3" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Database">#REF!</definedName>
@@ -67,7 +67,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.00000000000"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -104,12 +104,6 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -133,7 +127,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -147,9 +141,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -680,7 +671,7 @@
       <c r="A2">
         <v>201511</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="4">
         <v>95.211203063599996</v>
       </c>
       <c r="C2">
@@ -700,7 +691,7 @@
       <c r="A3">
         <v>201512</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="4">
         <v>100.169376594</v>
       </c>
       <c r="C3">
@@ -720,7 +711,7 @@
       <c r="A4">
         <v>201601</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="4">
         <v>43.714411116000001</v>
       </c>
       <c r="C4">
@@ -740,7 +731,7 @@
       <c r="A5">
         <v>201602</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="4">
         <v>82.795110329699995</v>
       </c>
       <c r="C5">
@@ -760,7 +751,7 @@
       <c r="A6">
         <v>201603</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="4">
         <v>48.451558003300001</v>
       </c>
       <c r="C6">
@@ -797,7 +788,7 @@
       <c r="A8">
         <v>201605</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C8">
@@ -817,7 +808,7 @@
       <c r="A9">
         <v>201606</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C9">
@@ -837,7 +828,7 @@
       <c r="A10">
         <v>201607</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10" s="4">
         <v>36.953880826400002</v>
       </c>
       <c r="C10">
@@ -857,7 +848,7 @@
       <c r="A11">
         <v>201608</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B11" s="4">
         <v>65.818416223100002</v>
       </c>
       <c r="C11">
@@ -877,7 +868,7 @@
       <c r="A12">
         <v>201609</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B12" s="4">
         <v>62.735856343000002</v>
       </c>
       <c r="C12">
@@ -914,7 +905,7 @@
       <c r="A14">
         <v>201611</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B14" s="4">
         <v>19.982324278</v>
       </c>
       <c r="C14">
@@ -934,7 +925,7 @@
       <c r="A15">
         <v>201612</v>
       </c>
-      <c r="B15" s="5">
+      <c r="B15" s="4">
         <v>25.422895852900002</v>
       </c>
       <c r="C15">
@@ -954,7 +945,7 @@
       <c r="A16">
         <v>201701</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C16">
@@ -974,7 +965,7 @@
       <c r="A17">
         <v>201702</v>
       </c>
-      <c r="B17" s="5">
+      <c r="B17" s="4">
         <v>64.142904082699999</v>
       </c>
       <c r="C17">
@@ -1011,7 +1002,7 @@
       <c r="A19">
         <v>201704</v>
       </c>
-      <c r="B19" s="5">
+      <c r="B19" s="4">
         <v>77.378337211300007</v>
       </c>
       <c r="C19">
@@ -1031,7 +1022,7 @@
       <c r="A20">
         <v>201705</v>
       </c>
-      <c r="B20" s="5">
+      <c r="B20" s="4">
         <v>75.829272940699994</v>
       </c>
       <c r="C20">
@@ -1051,7 +1042,7 @@
       <c r="A21">
         <v>201706</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C21">
@@ -1071,7 +1062,7 @@
       <c r="A22">
         <v>201707</v>
       </c>
-      <c r="B22" s="5">
+      <c r="B22" s="4">
         <v>93.242167954199999</v>
       </c>
       <c r="C22">
@@ -1091,7 +1082,7 @@
       <c r="A23">
         <v>201708</v>
       </c>
-      <c r="B23" s="5">
+      <c r="B23" s="4">
         <v>56.1302843482</v>
       </c>
       <c r="C23">
@@ -1111,7 +1102,7 @@
       <c r="A24">
         <v>201709</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C24">
@@ -1131,7 +1122,7 @@
       <c r="A25">
         <v>201710</v>
       </c>
-      <c r="B25" s="5">
+      <c r="B25" s="4">
         <v>52.306217843299997</v>
       </c>
       <c r="C25">
@@ -1151,7 +1142,7 @@
       <c r="A26">
         <v>201711</v>
       </c>
-      <c r="B26" s="5">
+      <c r="B26" s="4">
         <v>58.661662564399997</v>
       </c>
       <c r="C26">
@@ -1171,7 +1162,7 @@
       <c r="A27">
         <v>201712</v>
       </c>
-      <c r="B27" s="5">
+      <c r="B27" s="4">
         <v>48.242591755500001</v>
       </c>
       <c r="C27">
@@ -1191,7 +1182,7 @@
       <c r="A28">
         <v>201801</v>
       </c>
-      <c r="B28" s="5">
+      <c r="B28" s="4">
         <v>72.260339135699994</v>
       </c>
       <c r="C28">
@@ -1211,7 +1202,7 @@
       <c r="A29">
         <v>201802</v>
       </c>
-      <c r="B29" s="5">
+      <c r="B29" s="4">
         <v>51.387023458199998</v>
       </c>
       <c r="C29">
@@ -1231,7 +1222,7 @@
       <c r="A30">
         <v>201803</v>
       </c>
-      <c r="B30" s="5">
+      <c r="B30" s="4">
         <v>37.662006108500002</v>
       </c>
       <c r="C30">
@@ -1251,7 +1242,7 @@
       <c r="A31">
         <v>201804</v>
       </c>
-      <c r="B31" s="5">
+      <c r="B31" s="4">
         <v>76.565945685399996</v>
       </c>
       <c r="C31">
@@ -1271,7 +1262,7 @@
       <c r="A32">
         <v>201805</v>
       </c>
-      <c r="B32" s="5">
+      <c r="B32" s="4">
         <v>51.9941378539</v>
       </c>
       <c r="C32">
@@ -1291,7 +1282,7 @@
       <c r="A33">
         <v>201806</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C33">
@@ -1311,7 +1302,7 @@
       <c r="A34">
         <v>201807</v>
       </c>
-      <c r="B34" s="5">
+      <c r="B34" s="4">
         <v>46.983730104300001</v>
       </c>
       <c r="C34">
@@ -1331,7 +1322,7 @@
       <c r="A35">
         <v>201808</v>
       </c>
-      <c r="B35" s="5">
+      <c r="B35" s="4">
         <v>61.363854763500001</v>
       </c>
       <c r="C35">
@@ -1351,7 +1342,7 @@
       <c r="A36">
         <v>201809</v>
       </c>
-      <c r="B36" s="5">
+      <c r="B36" s="4">
         <v>69.140919002900006</v>
       </c>
       <c r="C36">
@@ -1371,7 +1362,7 @@
       <c r="A37">
         <v>201810</v>
       </c>
-      <c r="B37" s="5">
+      <c r="B37" s="4">
         <v>57.3642265971</v>
       </c>
       <c r="C37">
@@ -1391,7 +1382,7 @@
       <c r="A38">
         <v>201811</v>
       </c>
-      <c r="B38" s="5">
+      <c r="B38" s="4">
         <v>43.029706547000004</v>
       </c>
       <c r="C38">
@@ -1411,7 +1402,7 @@
       <c r="A39">
         <v>201812</v>
       </c>
-      <c r="B39" s="5">
+      <c r="B39" s="4">
         <v>45.047299963199997</v>
       </c>
       <c r="C39">
@@ -1431,7 +1422,7 @@
       <c r="A40">
         <v>201901</v>
       </c>
-      <c r="B40" s="5">
+      <c r="B40" s="4">
         <v>34.5054754708</v>
       </c>
       <c r="C40">
@@ -1451,7 +1442,7 @@
       <c r="A41">
         <v>201902</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="B41" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C41">
@@ -1471,7 +1462,7 @@
       <c r="A42">
         <v>201903</v>
       </c>
-      <c r="B42" s="5">
+      <c r="B42" s="4">
         <v>72.805503853700003</v>
       </c>
       <c r="C42">
@@ -1491,7 +1482,7 @@
       <c r="A43">
         <v>201904</v>
       </c>
-      <c r="B43" s="5">
+      <c r="B43" s="4">
         <v>79.152739331899994</v>
       </c>
       <c r="C43">
@@ -1511,7 +1502,7 @@
       <c r="A44">
         <v>201905</v>
       </c>
-      <c r="B44" s="5">
+      <c r="B44" s="4">
         <v>104.924565832</v>
       </c>
       <c r="C44">
@@ -1531,7 +1522,7 @@
       <c r="A45">
         <v>201906</v>
       </c>
-      <c r="B45" s="5">
+      <c r="B45" s="4">
         <v>74.330743690700004</v>
       </c>
       <c r="C45">
@@ -1551,7 +1542,7 @@
       <c r="A46">
         <v>201907</v>
       </c>
-      <c r="B46" s="5">
+      <c r="B46" s="4">
         <v>54.006911089799999</v>
       </c>
       <c r="C46">
@@ -1571,7 +1562,7 @@
       <c r="A47">
         <v>201908</v>
       </c>
-      <c r="B47" s="5">
+      <c r="B47" s="4">
         <v>75.618094814399996</v>
       </c>
       <c r="C47">
@@ -1591,7 +1582,7 @@
       <c r="A48">
         <v>201909</v>
       </c>
-      <c r="B48" s="5">
+      <c r="B48" s="4">
         <v>63.442879605199998</v>
       </c>
       <c r="C48">
@@ -1611,7 +1602,7 @@
       <c r="A49">
         <v>201910</v>
       </c>
-      <c r="B49" s="5">
+      <c r="B49" s="4">
         <v>54.900858505099997</v>
       </c>
       <c r="C49">
@@ -1631,7 +1622,7 @@
       <c r="A50">
         <v>201911</v>
       </c>
-      <c r="B50" s="5">
+      <c r="B50" s="4">
         <v>56.363936510099997</v>
       </c>
       <c r="C50">
@@ -1651,7 +1642,7 @@
       <c r="A51">
         <v>201912</v>
       </c>
-      <c r="B51" s="5">
+      <c r="B51" s="4">
         <v>42.2139560687</v>
       </c>
       <c r="C51">
@@ -1671,7 +1662,7 @@
       <c r="A52">
         <v>202001</v>
       </c>
-      <c r="B52" s="5">
+      <c r="B52" s="4">
         <v>59.285482926999997</v>
       </c>
       <c r="C52">
@@ -1691,7 +1682,7 @@
       <c r="A53">
         <v>202002</v>
       </c>
-      <c r="B53" s="5">
+      <c r="B53" s="4">
         <v>78.812047304800004</v>
       </c>
       <c r="C53">
@@ -1711,7 +1702,7 @@
       <c r="A54">
         <v>202003</v>
       </c>
-      <c r="B54" s="5">
+      <c r="B54" s="4">
         <v>74.6179653194</v>
       </c>
       <c r="C54">
@@ -1731,7 +1722,7 @@
       <c r="A55">
         <v>202004</v>
       </c>
-      <c r="B55" s="5">
+      <c r="B55" s="4">
         <v>68.438001769899998</v>
       </c>
       <c r="C55">
@@ -1751,7 +1742,7 @@
       <c r="A56">
         <v>202005</v>
       </c>
-      <c r="B56" s="5">
+      <c r="B56" s="4">
         <v>74.652174591000005</v>
       </c>
       <c r="C56">
@@ -1771,7 +1762,7 @@
       <c r="A57">
         <v>202006</v>
       </c>
-      <c r="B57" s="5">
+      <c r="B57" s="4">
         <v>60.9135450112</v>
       </c>
       <c r="C57">
@@ -1791,7 +1782,7 @@
       <c r="A58">
         <v>202007</v>
       </c>
-      <c r="B58" s="5" t="s">
+      <c r="B58" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C58">
@@ -1811,7 +1802,7 @@
       <c r="A59">
         <v>202008</v>
       </c>
-      <c r="B59" s="5">
+      <c r="B59" s="4">
         <v>46.635975211199998</v>
       </c>
       <c r="C59">
@@ -1831,7 +1822,7 @@
       <c r="A60">
         <v>202009</v>
       </c>
-      <c r="B60" s="5">
+      <c r="B60" s="4">
         <v>66.919709188400006</v>
       </c>
       <c r="C60">
@@ -1851,7 +1842,7 @@
       <c r="A61">
         <v>202010</v>
       </c>
-      <c r="B61" s="5">
+      <c r="B61" s="4">
         <v>42.834083940699998</v>
       </c>
       <c r="C61">
@@ -1871,7 +1862,7 @@
       <c r="A62">
         <v>202011</v>
       </c>
-      <c r="B62" s="5">
+      <c r="B62" s="4">
         <v>28.590436161900001</v>
       </c>
       <c r="C62">
@@ -1891,7 +1882,7 @@
       <c r="A63">
         <v>202012</v>
       </c>
-      <c r="B63" s="5">
+      <c r="B63" s="4">
         <v>26.161863597699998</v>
       </c>
       <c r="C63">
@@ -1911,7 +1902,7 @@
       <c r="A64">
         <v>202101</v>
       </c>
-      <c r="B64" s="5">
+      <c r="B64" s="4">
         <v>53.315313353900002</v>
       </c>
       <c r="C64">
@@ -1931,7 +1922,7 @@
       <c r="A65">
         <v>202102</v>
       </c>
-      <c r="B65" s="5">
+      <c r="B65" s="4">
         <v>16.062260638000001</v>
       </c>
       <c r="C65">
@@ -1951,7 +1942,7 @@
       <c r="A66">
         <v>202103</v>
       </c>
-      <c r="B66" s="5">
+      <c r="B66" s="4">
         <v>51.523118885099997</v>
       </c>
       <c r="C66">
@@ -1971,7 +1962,7 @@
       <c r="A67">
         <v>202104</v>
       </c>
-      <c r="B67" s="5">
+      <c r="B67" s="4">
         <v>59.658287818600002</v>
       </c>
       <c r="C67">
@@ -1991,7 +1982,7 @@
       <c r="A68">
         <v>202105</v>
       </c>
-      <c r="B68" s="5">
+      <c r="B68" s="4">
         <v>97.213859014099995</v>
       </c>
       <c r="C68">
@@ -2011,7 +2002,7 @@
       <c r="A69">
         <v>202106</v>
       </c>
-      <c r="B69" s="5">
+      <c r="B69" s="4">
         <v>81.384476668700003</v>
       </c>
       <c r="C69">
@@ -2031,7 +2022,7 @@
       <c r="A70">
         <v>202107</v>
       </c>
-      <c r="B70" s="5">
+      <c r="B70" s="4">
         <v>90.164123854699994</v>
       </c>
       <c r="C70">
@@ -2051,7 +2042,7 @@
       <c r="A71">
         <v>202108</v>
       </c>
-      <c r="B71" s="5">
+      <c r="B71" s="4">
         <v>40.253743393699999</v>
       </c>
       <c r="C71">
@@ -2071,7 +2062,7 @@
       <c r="A72">
         <v>202109</v>
       </c>
-      <c r="B72" s="5">
+      <c r="B72" s="4">
         <v>48.769122515500001</v>
       </c>
       <c r="C72">
@@ -2091,7 +2082,7 @@
       <c r="A73">
         <v>202110</v>
       </c>
-      <c r="B73" s="5">
+      <c r="B73" s="4">
         <v>40.782701576100003</v>
       </c>
       <c r="C73">
@@ -2111,7 +2102,7 @@
       <c r="A74">
         <v>202111</v>
       </c>
-      <c r="B74" s="5">
+      <c r="B74" s="4">
         <v>49.362960362700001</v>
       </c>
       <c r="C74">
@@ -2131,7 +2122,7 @@
       <c r="A75">
         <v>202112</v>
       </c>
-      <c r="B75" s="5">
+      <c r="B75" s="4">
         <v>43.653362586299998</v>
       </c>
       <c r="C75">
@@ -2151,7 +2142,7 @@
       <c r="A76">
         <v>202201</v>
       </c>
-      <c r="B76" s="5">
+      <c r="B76" s="4">
         <v>42.738602202999999</v>
       </c>
       <c r="C76">
@@ -2171,7 +2162,7 @@
       <c r="A77">
         <v>202202</v>
       </c>
-      <c r="B77" s="5">
+      <c r="B77" s="4">
         <v>74.878377232700004</v>
       </c>
       <c r="C77">
@@ -2191,7 +2182,7 @@
       <c r="A78">
         <v>202203</v>
       </c>
-      <c r="B78" s="5">
+      <c r="B78" s="4">
         <v>84.390307323200005</v>
       </c>
       <c r="C78">
@@ -2211,7 +2202,7 @@
       <c r="A79">
         <v>202204</v>
       </c>
-      <c r="B79" s="5">
+      <c r="B79" s="4">
         <v>88.084750116500004</v>
       </c>
       <c r="C79">
@@ -2231,7 +2222,7 @@
       <c r="A80">
         <v>202205</v>
       </c>
-      <c r="B80" s="5">
+      <c r="B80" s="4">
         <v>93.587813837599995</v>
       </c>
       <c r="C80">
@@ -2251,7 +2242,7 @@
       <c r="A81">
         <v>202206</v>
       </c>
-      <c r="B81" s="5" t="s">
+      <c r="B81" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C81">
@@ -2271,7 +2262,7 @@
       <c r="A82">
         <v>202207</v>
       </c>
-      <c r="B82" s="5">
+      <c r="B82" s="4">
         <v>96.949746443199999</v>
       </c>
       <c r="C82">
@@ -2291,7 +2282,7 @@
       <c r="A83">
         <v>202208</v>
       </c>
-      <c r="B83" s="5">
+      <c r="B83" s="4">
         <v>95.397317467700006</v>
       </c>
       <c r="C83">
@@ -2311,7 +2302,7 @@
       <c r="A84">
         <v>202209</v>
       </c>
-      <c r="B84" s="5">
+      <c r="B84" s="4">
         <v>111.16778368200001</v>
       </c>
       <c r="C84">
@@ -2331,7 +2322,7 @@
       <c r="A85">
         <v>202210</v>
       </c>
-      <c r="B85" s="5">
+      <c r="B85" s="4">
         <v>82.736862822500001</v>
       </c>
       <c r="C85">
@@ -2351,7 +2342,7 @@
       <c r="A86">
         <v>202211</v>
       </c>
-      <c r="B86" s="5">
+      <c r="B86" s="4">
         <v>71.380675108899993</v>
       </c>
       <c r="C86">
@@ -2371,7 +2362,7 @@
       <c r="A87">
         <v>202212</v>
       </c>
-      <c r="B87" s="5">
+      <c r="B87" s="4">
         <v>83.096626649000001</v>
       </c>
       <c r="C87">
@@ -2391,7 +2382,7 @@
       <c r="A88">
         <v>202301</v>
       </c>
-      <c r="B88" s="5">
+      <c r="B88" s="4">
         <v>78.263426021599997</v>
       </c>
       <c r="C88">
@@ -2411,7 +2402,7 @@
       <c r="A89">
         <v>202302</v>
       </c>
-      <c r="B89" s="5">
+      <c r="B89" s="4">
         <v>65.204282448800001</v>
       </c>
       <c r="C89">
@@ -2431,7 +2422,7 @@
       <c r="A90">
         <v>202303</v>
       </c>
-      <c r="B90" s="5">
+      <c r="B90" s="4">
         <v>73.572694006399999</v>
       </c>
       <c r="C90">
@@ -2451,7 +2442,7 @@
       <c r="A91">
         <v>202304</v>
       </c>
-      <c r="B91" s="5">
+      <c r="B91" s="4">
         <v>69.607860420799994</v>
       </c>
       <c r="C91">
@@ -2471,7 +2462,7 @@
       <c r="A92">
         <v>202305</v>
       </c>
-      <c r="B92" s="5">
+      <c r="B92" s="4">
         <v>59.096275865300001</v>
       </c>
       <c r="C92">
@@ -2491,7 +2482,7 @@
       <c r="A93">
         <v>202306</v>
       </c>
-      <c r="B93" s="5" t="s">
+      <c r="B93" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C93">
@@ -2511,8 +2502,8 @@
       <c r="A94">
         <v>202307</v>
       </c>
-      <c r="B94" s="5">
-        <v>97.880598833999997</v>
+      <c r="B94" s="4">
+        <v>84.292997434300005</v>
       </c>
       <c r="C94">
         <v>24.901</v>
@@ -2531,8 +2522,8 @@
       <c r="A95">
         <v>202308</v>
       </c>
-      <c r="B95" s="5">
-        <v>77.910641370199997</v>
+      <c r="B95" s="4">
+        <v>44.0537375838</v>
       </c>
       <c r="C95">
         <v>15.27</v>
@@ -2552,7 +2543,7 @@
         <v>202309</v>
       </c>
       <c r="B96" s="4">
-        <v>80.946137409900004</v>
+        <v>38.223572840999999</v>
       </c>
       <c r="C96">
         <v>13.159000000000001</v>
@@ -2572,7 +2563,7 @@
         <v>202310</v>
       </c>
       <c r="B97" s="4">
-        <v>78.031118549799999</v>
+        <v>23.603315077800001</v>
       </c>
       <c r="C97">
         <v>1.843</v>
@@ -2592,7 +2583,7 @@
         <v>202311</v>
       </c>
       <c r="B98" s="4">
-        <v>75.297598763699995</v>
+        <v>21.921391910699999</v>
       </c>
       <c r="C98">
         <v>3.532</v>
@@ -2609,7 +2600,7 @@
         <v>202312</v>
       </c>
       <c r="B99" s="4">
-        <v>67.976891408</v>
+        <v>6.2728212450300003</v>
       </c>
       <c r="C99">
         <v>4.1360000000000001</v>
